--- a/data/processed/sakila/metrics/combined_search_top_5_respective.xlsx
+++ b/data/processed/sakila/metrics/combined_search_top_5_respective.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4627861595683376</v>
+        <v>0.4399889988998897</v>
       </c>
       <c r="C2" t="n">
         <v>0.4399889988998897</v>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3468280161349467</v>
+        <v>0.3267876787678767</v>
       </c>
       <c r="C3" t="n">
         <v>0.3267876787678767</v>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3513594216564513</v>
+        <v>0.3313531353135314</v>
       </c>
       <c r="C4" t="n">
         <v>0.3313531353135314</v>
